--- a/EKG_Kalite_Yönetim_Sistemi/04_Parça ve Proses Kontrolü/04_Laboratuvar, COP ve Test Kapsamı/EKG-KLT-LST-04_ic_laboratuvar_kapsami_test_metotlari_ve_yetkili_person.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/04_Parça ve Proses Kontrolü/04_Laboratuvar, COP ve Test Kapsamı/EKG-KLT-LST-04_ic_laboratuvar_kapsami_test_metotlari_ve_yetkili_person.xlsx
@@ -710,7 +710,7 @@
       <x:c r="B9" s="8"/>
       <x:c r="C9" s="9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">04.05.2026</x:t>
+          <x:t xml:space="preserve">10.06.2026</x:t>
         </x:is>
       </x:c>
       <x:c r="D9" s="9"/>
@@ -966,7 +966,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-LST-04&amp;C&amp;"Arial,Regular"&amp;11İç Laboratuvar Kapsamı, Test Metotları ve Yetkili Personel Listesi</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 21.09.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9837b46ab544a8c"/>
   <x:tableParts count="1">
@@ -1323,7 +1324,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-LST-04&amp;C&amp;"Arial,Regular"&amp;11İç Laboratuvar Kapsamı, Test Metotları ve Yetkili Personel Listesi</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 21.09.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R418da034f80945c4"/>
   <x:tableParts count="1">
@@ -1627,7 +1629,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-LST-04&amp;C&amp;"Arial,Regular"&amp;11İç Laboratuvar Kapsamı, Test Metotları ve Yetkili Personel Listesi</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 21.09.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15ea0b7fccb64593"/>
   <x:tableParts count="1">
